--- a/Homework 1.xlsx
+++ b/Homework 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/814ef5049b916cec/School Documents/Fall 2025/CHE 1311 and 1411L/1311/HW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/814ef5049b916cec/School Documents/Fall 2025/CHE 1311 and 1411L/1411L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1247" documentId="8_{A4498D15-3607-F74A-B2E9-A9841357A743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD647646-234C-4F31-8C87-DCD92C489F1D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{515355BC-9A8C-A446-B4CE-B6938F1E4E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7845" yWindow="0" windowWidth="21060" windowHeight="7845" activeTab="2" xr2:uid="{2E48908D-70EC-CF42-9BCD-02F1A654E1EE}"/>
+    <workbookView xWindow="4000" yWindow="600" windowWidth="21600" windowHeight="11300" activeTab="4" xr2:uid="{2E48908D-70EC-CF42-9BCD-02F1A654E1EE}"/>
   </bookViews>
   <sheets>
     <sheet name="2.11" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>Calculates the Area and Volume of a Cylinder</t>
   </si>
@@ -265,9 +265,6 @@
   </si>
   <si>
     <t>Oil Temp</t>
-  </si>
-  <si>
-    <t>($C$4)+(($C$3-$C$4)* EXP((-B9)/$C$5))</t>
   </si>
 </sst>
 </file>
@@ -2061,7 +2058,7 @@
                   <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>784.57476650596232</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>769.45497309965981</c:v>
@@ -11481,20 +11478,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355DEAC0-2C53-5240-BAB3-A17A4A2E59BF}">
   <dimension ref="B1:C8"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.125" customWidth="1"/>
-    <col min="3" max="3" width="18.625" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="73" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="73"/>
     </row>
-    <row r="3" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -11502,7 +11499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -11510,7 +11507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
@@ -11518,11 +11515,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="31"/>
       <c r="C6" s="30"/>
     </row>
-    <row r="7" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
@@ -11531,7 +11528,7 @@
         <v>219.91148575128551</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
@@ -11557,17 +11554,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37FC076-D301-425C-A821-7961F6F692E0}">
   <dimension ref="B1:E7"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.125" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="74" t="s">
         <v>7</v>
       </c>
@@ -11575,7 +11572,7 @@
       <c r="D2" s="75"/>
       <c r="E2" s="76"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B3" s="77" t="s">
         <v>8</v>
       </c>
@@ -11585,7 +11582,7 @@
       </c>
       <c r="E3" s="78"/>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B4" s="14" t="s">
         <v>10</v>
       </c>
@@ -11600,7 +11597,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" s="14" t="s">
         <v>11</v>
       </c>
@@ -11615,7 +11612,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
@@ -11630,7 +11627,7 @@
         <v>22.241108075</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18" t="s">
         <v>13</v>
       </c>
@@ -11658,20 +11655,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A033B096-6C1C-44A9-BEA8-ABD60EACE5B8}">
   <dimension ref="B1:C188"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="79" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="80"/>
     </row>
-    <row r="3" spans="2:3" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="24" t="s">
         <v>22</v>
       </c>
@@ -11679,7 +11676,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
         <v>21</v>
       </c>
@@ -11687,7 +11684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="s">
         <v>20</v>
       </c>
@@ -11695,7 +11692,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
         <v>19</v>
       </c>
@@ -11703,7 +11700,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
         <v>0</v>
       </c>
@@ -11712,24 +11709,25 @@
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" s="4">
         <v>1</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="9">
+        <f t="shared" ref="C9:C72" si="0">($C$4)+(($C$3-$C$4)* EXP((-B9)/$C$5))</f>
+        <v>784.57476650596232</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" s="4">
         <v>2</v>
       </c>
       <c r="C10" s="9">
-        <f t="shared" ref="C9:C72" si="0">($C$4)+(($C$3-$C$4)* EXP((-B10)/$C$5))</f>
+        <f t="shared" si="0"/>
         <v>769.45497309965981</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" s="4">
         <v>3</v>
       </c>
@@ -11738,7 +11736,7 @@
         <v>754.6345716621297</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" s="4">
         <v>4</v>
       </c>
@@ -11747,7 +11745,7 @@
         <v>740.10763383518929</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" s="4">
         <v>5</v>
       </c>
@@ -11756,7 +11754,7 @@
         <v>725.86834865001242</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" s="4">
         <v>6</v>
       </c>
@@ -11765,7 +11763,7 @@
         <v>711.91102020266567</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" s="4">
         <v>7</v>
       </c>
@@ -11774,7 +11772,7 @@
         <v>698.23006537566971</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" s="4">
         <v>8</v>
       </c>
@@ -11783,7 +11781,7 @@
         <v>684.8200116046786</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="4">
         <v>9</v>
       </c>
@@ -11792,7 +11790,7 @@
         <v>671.67549468938091</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="4">
         <v>10</v>
       </c>
@@ -11801,7 +11799,7 @@
         <v>658.79125664774779</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="4">
         <v>11</v>
       </c>
@@ -11810,7 +11808,7 @@
         <v>646.16214361277071</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="4">
         <v>12</v>
       </c>
@@ -11819,7 +11817,7 @@
         <v>633.78310377084517</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="4">
         <v>13</v>
       </c>
@@ -11828,7 +11826,7 @@
         <v>621.64918534097808</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="4">
         <v>14</v>
       </c>
@@ -11837,7 +11835,7 @@
         <v>609.7555345940101</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="4">
         <v>15</v>
       </c>
@@ -11846,7 +11844,7 @@
         <v>598.09739391105825</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="4">
         <v>16</v>
       </c>
@@ -11855,7 +11853,7 @@
         <v>586.67009988040525</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" s="4">
         <v>17</v>
       </c>
@@ -11864,7 +11862,7 @@
         <v>575.46908143207293</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="4">
         <v>18</v>
       </c>
@@ -11873,7 +11871,7 @@
         <v>564.48985800933315</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" s="4">
         <v>19</v>
       </c>
@@ -11882,7 +11880,7 @@
         <v>553.72803777642514</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" s="4">
         <v>20</v>
       </c>
@@ -11891,7 +11889,7 @@
         <v>543.17931586176303</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29" s="4">
         <v>21</v>
       </c>
@@ -11900,7 +11898,7 @@
         <v>532.83947263592927</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" s="4">
         <v>22</v>
       </c>
@@ -11909,7 +11907,7 @@
         <v>522.70437202376718</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B31" s="4">
         <v>23</v>
       </c>
@@ -11918,7 +11916,7 @@
         <v>512.76995984989526</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" s="4">
         <v>24</v>
       </c>
@@ -11927,7 +11925,7 @@
         <v>503.03226221698372</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" s="4">
         <v>25</v>
       </c>
@@ -11936,7 +11934,7 @@
         <v>493.48738391614143</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34" s="4">
         <v>26</v>
       </c>
@@ -11945,7 +11943,7 @@
         <v>484.1315068687814</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" s="4">
         <v>27</v>
       </c>
@@ -11954,7 +11952,7 @@
         <v>474.96088859933792</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B36" s="4">
         <v>28</v>
       </c>
@@ -11963,7 +11961,7 @@
         <v>465.97186073822678</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37" s="4">
         <v>29</v>
       </c>
@@ -11972,7 +11970,7 @@
         <v>457.16082755444819</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38" s="4">
         <v>30</v>
       </c>
@@ -11981,7 +11979,7 @@
         <v>448.52426451724654</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B39" s="4">
         <v>31</v>
       </c>
@@ -11990,7 +11988,7 @@
         <v>440.05871688625143</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B40" s="4">
         <v>32</v>
       </c>
@@ -11999,7 +11997,7 @@
         <v>431.76079832953479</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B41" s="4">
         <v>33</v>
       </c>
@@ -12008,7 +12006,7 @@
         <v>423.62718956903365</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B42" s="4">
         <v>34</v>
       </c>
@@ -12017,7 +12015,7 @@
         <v>415.65463705279427</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B43" s="4">
         <v>35</v>
       </c>
@@ -12026,7 +12024,7 @@
         <v>407.83995165350802</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B44" s="4">
         <v>36</v>
       </c>
@@ -12035,7 +12033,7 @@
         <v>400.18000739281791</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B45" s="4">
         <v>37</v>
       </c>
@@ -12044,7 +12042,7 @@
         <v>392.67174019088577</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B46" s="4">
         <v>38</v>
       </c>
@@ -12053,7 +12051,7 @@
         <v>385.31214664071928</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B47" s="4">
         <v>39</v>
       </c>
@@ -12062,7 +12060,7 @@
         <v>378.09828280676913</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B48" s="4">
         <v>40</v>
       </c>
@@ -12071,7 +12069,7 @@
         <v>371.02726304731561</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" s="4">
         <v>41</v>
       </c>
@@ -12080,7 +12078,7 @@
         <v>364.09625886017346</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="4">
         <v>42</v>
       </c>
@@ -12089,7 +12087,7 @@
         <v>357.3024977512531</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="4">
         <v>43</v>
       </c>
@@ -12098,7 +12096,7 @@
         <v>350.64326212552635</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="4">
         <v>44</v>
       </c>
@@ -12107,7 +12105,7 @@
         <v>344.11588819995188</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="4">
         <v>45</v>
       </c>
@@ -12116,7 +12114,7 @@
         <v>337.71776493792669</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="4">
         <v>46</v>
       </c>
@@ -12125,7 +12123,7 @@
         <v>331.4463330048365</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="4">
         <v>47</v>
       </c>
@@ -12134,7 +12132,7 @@
         <v>325.29908374428794</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="4">
         <v>48</v>
       </c>
@@ -12143,7 +12141,7 @@
         <v>319.27355817461228</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="4">
         <v>49</v>
       </c>
@@ -12152,7 +12150,7 @@
         <v>313.36734600524028</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="4">
         <v>50</v>
       </c>
@@ -12161,7 +12159,7 @@
         <v>307.57808467255359</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="4">
         <v>51</v>
       </c>
@@ -12170,7 +12168,7 @@
         <v>301.90345839482802</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="4">
         <v>52</v>
       </c>
@@ -12179,7 +12177,7 @@
         <v>296.34119724588976</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="4">
         <v>53</v>
       </c>
@@ -12188,7 +12186,7 @@
         <v>290.8890762471147</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" s="4">
         <v>54</v>
       </c>
@@ -12197,7 +12195,7 @@
         <v>285.54491447740759</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63" s="4">
         <v>55</v>
       </c>
@@ -12206,7 +12204,7 @@
         <v>280.30657420080399</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="4">
         <v>56</v>
       </c>
@@ -12215,7 +12213,7 @@
         <v>275.17196001134778</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" s="4">
         <v>57</v>
       </c>
@@ -12224,7 +12222,7 @@
         <v>270.13901799490077</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" s="4">
         <v>58</v>
       </c>
@@ -12233,7 +12231,7 @@
         <v>265.20573490754953</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B67" s="4">
         <v>59</v>
       </c>
@@ -12242,7 +12240,7 @@
         <v>260.37013737028121</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B68" s="4">
         <v>60</v>
       </c>
@@ -12251,7 +12249,7 @@
         <v>255.63029107960546</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B69" s="4">
         <v>61</v>
       </c>
@@ -12260,7 +12258,7 @@
         <v>250.98430003380707</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B70" s="4">
         <v>62</v>
       </c>
@@ -12269,7 +12267,7 @@
         <v>246.43030577452043</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B71" s="4">
         <v>63</v>
       </c>
@@ -12278,7 +12276,7 @@
         <v>241.96648664332113</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B72" s="4">
         <v>64</v>
       </c>
@@ -12287,7 +12285,7 @@
         <v>237.59105705303824</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B73" s="4">
         <v>65</v>
       </c>
@@ -12296,7 +12294,7 @@
         <v>233.3022667734958</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="4">
         <v>66</v>
       </c>
@@ -12305,7 +12303,7 @@
         <v>229.09840023139742</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B75" s="4">
         <v>67</v>
       </c>
@@ -12314,7 +12312,7 @@
         <v>224.97777582407394</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B76" s="4">
         <v>68</v>
       </c>
@@ -12323,7 +12321,7 @@
         <v>220.93874524682002</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B77" s="4">
         <v>69</v>
       </c>
@@ -12332,7 +12330,7 @@
         <v>216.97969283355033</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B78" s="4">
         <v>70</v>
       </c>
@@ -12341,7 +12339,7 @@
         <v>213.09903491051145</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B79" s="4">
         <v>71</v>
       </c>
@@ -12350,7 +12348,7 @@
         <v>209.2952191627914</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B80" s="4">
         <v>72</v>
       </c>
@@ -12359,7 +12357,7 @@
         <v>205.56672401337286</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B81" s="4">
         <v>73</v>
       </c>
@@ -12368,7 +12366,7 @@
         <v>201.91205801448214</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B82" s="4">
         <v>74</v>
       </c>
@@ -12377,7 +12375,7 @@
         <v>198.32975925099012</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B83" s="4">
         <v>75</v>
       </c>
@@ -12386,7 +12384,7 @@
         <v>194.81839475562683</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B84" s="4">
         <v>76</v>
       </c>
@@ -12395,7 +12393,7 @@
         <v>191.37655993577528</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B85" s="4">
         <v>77</v>
       </c>
@@ -12404,7 +12402,7 @@
         <v>188.00287801161582</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B86" s="4">
         <v>78</v>
       </c>
@@ -12413,7 +12411,7 @@
         <v>184.69599946539572</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B87" s="4">
         <v>79</v>
       </c>
@@ -12422,7 +12420,7 @@
         <v>181.4546015016042</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B88" s="4">
         <v>80</v>
       </c>
@@ -12431,7 +12429,7 @@
         <v>178.27738751783653</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B89" s="4">
         <v>81</v>
       </c>
@@ -12440,7 +12438,7 @@
         <v>175.16308658613582</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B90" s="4">
         <v>82</v>
       </c>
@@ -12449,7 +12447,7 @@
         <v>172.11045294460479</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B91" s="4">
         <v>83</v>
       </c>
@@ -12458,7 +12456,7 @@
         <v>169.11826549908452</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B92" s="4">
         <v>84</v>
       </c>
@@ -12467,7 +12465,7 @@
         <v>166.18532733470036</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B93" s="4">
         <v>85</v>
       </c>
@@ -12476,7 +12474,7 @@
         <v>163.31046523708031</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B94" s="4">
         <v>86</v>
       </c>
@@ -12485,7 +12483,7 @@
         <v>160.49252922305322</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B95" s="4">
         <v>87</v>
       </c>
@@ -12494,7 +12492,7 @@
         <v>157.73039208064057</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96" s="4">
         <v>88</v>
       </c>
@@ -12503,7 +12501,7 @@
         <v>155.02294891815637</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B97" s="4">
         <v>89</v>
       </c>
@@ -12512,7 +12510,7 @@
         <v>152.3691167222359</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B98" s="4">
         <v>90</v>
       </c>
@@ -12521,7 +12519,7 @@
         <v>149.7678339246159</v>
       </c>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B99" s="4">
         <v>91</v>
       </c>
@@ -12530,7 +12528,7 @@
         <v>147.21805997749311</v>
       </c>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B100" s="4">
         <v>92</v>
       </c>
@@ -12539,7 +12537,7 @@
         <v>144.71877493729122</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B101" s="4">
         <v>93</v>
       </c>
@@ -12548,7 +12546,7 @@
         <v>142.26897905666991</v>
       </c>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B102" s="4">
         <v>94</v>
       </c>
@@ -12557,7 +12555,7 @@
         <v>139.86769238461255</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B103" s="4">
         <v>95</v>
       </c>
@@ -12566,7 +12564,7 @@
         <v>137.51395437443273</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B104" s="4">
         <v>96</v>
       </c>
@@ -12575,7 +12573,7 @@
         <v>135.20682349954276</v>
       </c>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B105" s="4">
         <v>97</v>
       </c>
@@ -12584,7 +12582,7 @@
         <v>132.94537687683058</v>
       </c>
     </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B106" s="4">
         <v>98</v>
       </c>
@@ -12593,7 +12591,7 @@
         <v>130.72870989749407</v>
       </c>
     </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B107" s="4">
         <v>99</v>
       </c>
@@ -12602,7 +12600,7 @@
         <v>128.55593586518552</v>
       </c>
     </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B108" s="4">
         <v>100</v>
       </c>
@@ -12611,7 +12609,7 @@
         <v>126.4261856413213</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B109" s="4">
         <v>101</v>
       </c>
@@ -12620,7 +12618,7 @@
         <v>124.33860729741481</v>
       </c>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B110" s="4">
         <v>102</v>
       </c>
@@ -12629,7 +12627,7 @@
         <v>122.29236577429378</v>
       </c>
     </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B111" s="4">
         <v>103</v>
       </c>
@@ -12638,7 +12636,7 @@
         <v>120.28664254806536</v>
       </c>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B112" s="4">
         <v>104</v>
       </c>
@@ -12647,7 +12645,7 @@
         <v>118.32063530269571</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B113" s="4">
         <v>105</v>
       </c>
@@ -12656,7 +12654,7 @@
         <v>116.3935576090729</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B114" s="4">
         <v>106</v>
       </c>
@@ -12665,7 +12663,7 @@
         <v>114.50463861042479</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B115" s="4">
         <v>107</v>
       </c>
@@ -12674,7 +12672,7 @@
         <v>112.65312271396598</v>
       </c>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B116" s="4">
         <v>108</v>
       </c>
@@ -12683,7 +12681,7 @@
         <v>110.83826928865069</v>
       </c>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B117" s="4">
         <v>109</v>
       </c>
@@ -12692,7 +12690,7 @@
         <v>109.05935236891042</v>
       </c>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B118" s="4">
         <v>110</v>
       </c>
@@ -12701,7 +12699,7 @@
         <v>107.31566036425808</v>
       </c>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B119" s="4">
         <v>111</v>
       </c>
@@ -12710,7 +12708,7 @@
         <v>105.60649577464226</v>
       </c>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B120" s="4">
         <v>112</v>
       </c>
@@ -12719,7 +12717,7 @@
         <v>103.93117491143794</v>
       </c>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B121" s="4">
         <v>113</v>
       </c>
@@ -12728,7 +12726,7 @@
         <v>102.28902762396196</v>
       </c>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B122" s="4">
         <v>114</v>
       </c>
@@ -12737,7 +12735,7 @@
         <v>100.6793970314037</v>
       </c>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B123" s="4">
         <v>115</v>
       </c>
@@ -12746,7 +12744,7 @@
         <v>99.101639260064118</v>
       </c>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B124" s="4">
         <v>116</v>
       </c>
@@ -12755,7 +12753,7 @@
         <v>97.55512318579764</v>
       </c>
     </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B125" s="4">
         <v>117</v>
       </c>
@@ -12764,7 +12762,7 @@
         <v>96.039230181554075</v>
       </c>
     </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B126" s="4">
         <v>118</v>
       </c>
@@ -12773,7 +12771,7 @@
         <v>94.553353869919533</v>
       </c>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B127" s="4">
         <v>119</v>
       </c>
@@ -12782,7 +12780,7 @@
         <v>93.09689988055743</v>
       </c>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B128" s="4">
         <v>120</v>
       </c>
@@ -12791,7 +12789,7 @@
         <v>91.669285612452342</v>
       </c>
     </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B129" s="4">
         <v>121</v>
       </c>
@@ -12800,7 +12798,7 @@
         <v>90.269940000861965</v>
       </c>
     </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B130" s="4">
         <v>122</v>
       </c>
@@ -12809,7 +12807,7 @@
         <v>88.898303288883426</v>
       </c>
     </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B131" s="4">
         <v>123</v>
       </c>
@@ -12818,7 +12816,7 @@
         <v>87.553826803543245</v>
       </c>
     </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B132" s="4">
         <v>124</v>
       </c>
@@ -12827,7 +12825,7 @@
         <v>86.235972736320662</v>
       </c>
     </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B133" s="4">
         <v>125</v>
       </c>
@@ -12836,7 +12834,7 @@
         <v>84.944213928017163</v>
       </c>
     </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B134" s="4">
         <v>126</v>
       </c>
@@ -12845,7 +12843,7 @@
         <v>83.678033657885777</v>
       </c>
     </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B135" s="4">
         <v>127</v>
       </c>
@@ -12854,7 +12852,7 @@
         <v>82.43692543693578</v>
       </c>
     </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B136" s="4">
         <v>128</v>
       </c>
@@ -12863,7 +12861,7 @@
         <v>81.220392805330505</v>
       </c>
     </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B137" s="4">
         <v>129</v>
       </c>
@@ -12872,7 +12870,7 @@
         <v>80.027949133796625</v>
       </c>
     </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B138" s="4">
         <v>130</v>
       </c>
@@ -12881,7 +12879,7 @@
         <v>78.859117428966087</v>
       </c>
     </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B139" s="4">
         <v>131</v>
       </c>
@@ -12890,7 +12888,7 @@
         <v>77.713430142572321</v>
       </c>
     </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B140" s="4">
         <v>132</v>
       </c>
@@ -12899,7 +12897,7 @@
         <v>76.590428984424733</v>
       </c>
     </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B141" s="4">
         <v>133</v>
       </c>
@@ -12908,7 +12906,7 @@
         <v>75.489664739086521</v>
       </c>
     </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B142" s="4">
         <v>134</v>
       </c>
@@ -12917,7 +12915,7 @@
         <v>74.410697086182495</v>
       </c>
     </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B143" s="4">
         <v>135</v>
       </c>
@@ -12926,7 +12924,7 @@
         <v>73.353094424265066</v>
       </c>
     </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B144" s="4">
         <v>136</v>
       </c>
@@ -12935,7 +12933,7 @@
         <v>72.316433698167899</v>
       </c>
     </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B145" s="4">
         <v>137</v>
       </c>
@@ -12944,7 +12942,7 @@
         <v>71.30030022977823</v>
       </c>
     </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B146" s="4">
         <v>138</v>
       </c>
@@ -12953,7 +12951,7 @@
         <v>70.304287552160133</v>
       </c>
     </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B147" s="4">
         <v>139</v>
       </c>
@@ -12962,7 +12960,7 @@
         <v>69.327997246962127</v>
       </c>
     </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B148" s="4">
         <v>140</v>
       </c>
@@ -12971,7 +12969,7 @@
         <v>68.371038785044803</v>
       </c>
     </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B149" s="4">
         <v>141</v>
       </c>
@@ -12980,7 +12978,7 @@
         <v>67.433029370263768</v>
       </c>
     </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B150" s="4">
         <v>142</v>
       </c>
@@ -12989,7 +12987,7 @@
         <v>66.513593786346149</v>
       </c>
     </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B151" s="4">
         <v>143</v>
       </c>
@@ -12998,7 +12996,7 @@
         <v>65.612364246799075</v>
       </c>
     </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B152" s="4">
         <v>144</v>
       </c>
@@ -13007,7 +13005,7 @@
         <v>64.728980247790162</v>
       </c>
     </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B153" s="4">
         <v>145</v>
       </c>
@@ -13016,7 +13014,7 @@
         <v>63.863088423941235</v>
       </c>
     </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B154" s="4">
         <v>146</v>
       </c>
@@ -13025,7 +13023,7 @@
         <v>63.014342406977342</v>
       </c>
     </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B155" s="4">
         <v>147</v>
       </c>
@@ -13034,7 +13032,7 @@
         <v>62.182402687174935</v>
       </c>
     </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B156" s="4">
         <v>148</v>
       </c>
@@ -13043,7 +13041,7 @@
         <v>61.366936477553423</v>
       </c>
     </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B157" s="4">
         <v>149</v>
       </c>
@@ -13052,7 +13050,7 @@
         <v>60.567617580755936</v>
       </c>
     </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B158" s="4">
         <v>150</v>
       </c>
@@ -13061,7 +13059,7 @@
         <v>59.784126258566012</v>
       </c>
     </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B159" s="4">
         <v>151</v>
       </c>
@@ -13070,7 +13068,7 @@
         <v>59.0161491040081</v>
       </c>
     </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B160" s="4">
         <v>152</v>
       </c>
@@ -13079,7 +13077,7 @@
         <v>58.263378915980532</v>
       </c>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B161" s="4">
         <v>153</v>
       </c>
@@ -13088,7 +13086,7 @@
         <v>57.52551457637103</v>
       </c>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B162" s="4">
         <v>154</v>
       </c>
@@ -13097,7 +13095,7 @@
         <v>56.802260929605438</v>
       </c>
     </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B163" s="4">
         <v>155</v>
       </c>
@@ -13106,7 +13104,7 @@
         <v>56.093328664581527</v>
       </c>
     </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B164" s="4">
         <v>156</v>
       </c>
@@ -13115,7 +13113,7 @@
         <v>55.398434198940741</v>
       </c>
     </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B165" s="4">
         <v>157</v>
       </c>
@@ -13124,7 +13122,7 @@
         <v>54.717299565631436</v>
       </c>
     </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B166" s="4">
         <v>158</v>
       </c>
@@ -13133,7 +13131,7 @@
         <v>54.049652301718368</v>
       </c>
     </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B167" s="4">
         <v>159</v>
       </c>
@@ -13142,7 +13140,7 @@
         <v>53.395225339393889</v>
       </c>
     </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B168" s="4">
         <v>160</v>
       </c>
@@ -13151,7 +13149,7 @@
         <v>52.753756899147277</v>
       </c>
     </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B169" s="4">
         <v>161</v>
       </c>
@@ -13160,7 +13158,7 @@
         <v>52.124990385049387</v>
       </c>
     </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B170" s="4">
         <v>162</v>
       </c>
@@ -13169,7 +13167,7 @@
         <v>51.508674282110924</v>
       </c>
     </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B171" s="4">
         <v>163</v>
       </c>
@@ -13178,7 +13176,7 @@
         <v>50.904562055673068</v>
       </c>
     </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B172" s="4">
         <v>164</v>
       </c>
@@ -13187,7 +13185,7 @@
         <v>50.312412052790279</v>
       </c>
     </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B173" s="4">
         <v>165</v>
       </c>
@@ -13196,7 +13194,7 @@
         <v>49.731987405565974</v>
       </c>
     </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B174" s="4">
         <v>166</v>
       </c>
@@ -13205,7 +13203,7 @@
         <v>49.163055936402166</v>
       </c>
     </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B175" s="4">
         <v>167</v>
       </c>
@@ -13214,7 +13212,7 @@
         <v>48.605390065125341</v>
       </c>
     </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B176" s="4">
         <v>168</v>
       </c>
@@ -13223,7 +13221,7 @@
         <v>48.058766717951343</v>
       </c>
     </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B177" s="4">
         <v>169</v>
       </c>
@@ -13232,7 +13230,7 @@
         <v>47.522967238252889</v>
       </c>
     </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B178" s="4">
         <v>170</v>
       </c>
@@ -13241,7 +13239,7 @@
         <v>46.997777299094011</v>
       </c>
     </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B179" s="4">
         <v>171</v>
       </c>
@@ -13250,7 +13248,7 @@
         <v>46.482986817496439</v>
       </c>
     </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B180" s="4">
         <v>172</v>
       </c>
@@ -13259,7 +13257,7 @@
         <v>45.978389870403539</v>
       </c>
     </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B181" s="4">
         <v>173</v>
       </c>
@@ -13268,7 +13266,7 @@
         <v>45.483784612308447</v>
       </c>
     </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B182" s="4">
         <v>174</v>
       </c>
@@ -13277,7 +13275,7 @@
         <v>44.998973194513084</v>
       </c>
     </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B183" s="4">
         <v>175</v>
       </c>
@@ -13286,7 +13284,7 @@
         <v>44.523761685986116</v>
       </c>
     </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B184" s="4">
         <v>176</v>
       </c>
@@ -13295,7 +13293,7 @@
         <v>44.057959995787868</v>
       </c>
     </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B185" s="4">
         <v>177</v>
       </c>
@@ -13304,7 +13302,7 @@
         <v>43.601381797031507</v>
       </c>
     </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B186" s="4">
         <v>178</v>
       </c>
@@ -13313,7 +13311,7 @@
         <v>43.15384445234973</v>
       </c>
     </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B187" s="4">
         <v>179</v>
       </c>
@@ -13322,7 +13320,7 @@
         <v>42.71516894083743</v>
       </c>
     </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B188" s="10">
         <v>180</v>
       </c>
@@ -13346,14 +13344,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B056E1-DD1B-414A-9C56-BE84FC253301}">
   <dimension ref="B1:I17"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="s">
         <v>24</v>
       </c>
@@ -13367,7 +13365,7 @@
       <c r="H2" s="82"/>
       <c r="I2" s="84"/>
     </row>
-    <row r="3" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="31" t="s">
         <v>25</v>
       </c>
@@ -13393,7 +13391,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B4" s="33" t="s">
         <v>26</v>
       </c>
@@ -13419,7 +13417,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B5" s="37" t="s">
         <v>27</v>
       </c>
@@ -13445,7 +13443,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="37" t="s">
         <v>28</v>
       </c>
@@ -13471,7 +13469,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
         <v>29</v>
       </c>
@@ -13497,7 +13495,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="41" t="s">
         <v>34</v>
       </c>
@@ -13523,7 +13521,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -13533,7 +13531,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>31</v>
       </c>
@@ -13549,7 +13547,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>1</v>
       </c>
@@ -13567,7 +13565,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="46">
         <v>2</v>
       </c>
@@ -13585,7 +13583,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="46">
         <v>3</v>
       </c>
@@ -13603,7 +13601,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="46">
         <v>4</v>
       </c>
@@ -13621,7 +13619,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B15" s="46">
         <v>5</v>
       </c>
@@ -13639,7 +13637,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B16" s="46">
         <v>6</v>
       </c>
@@ -13657,7 +13655,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="49">
         <v>7</v>
       </c>
@@ -13689,19 +13687,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A7EF843-7F2A-4465-A0BB-B9FD0234CA4D}">
   <dimension ref="B1:H611"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.25" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" customWidth="1"/>
     <col min="7" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.875" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="85" t="s">
         <v>36</v>
       </c>
@@ -13714,7 +13712,7 @@
       <c r="G2" s="82"/>
       <c r="H2" s="84"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B3" s="67" t="s">
         <v>41</v>
       </c>
@@ -13735,7 +13733,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="37" t="s">
         <v>42</v>
       </c>
@@ -13758,7 +13756,7 @@
         <v>0.434</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B5" s="37" t="s">
         <v>37</v>
       </c>
@@ -13772,7 +13770,7 @@
       <c r="G5" s="55"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="37" t="s">
         <v>38</v>
       </c>
@@ -13785,7 +13783,7 @@
       <c r="E6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
         <v>39</v>
       </c>
@@ -13805,7 +13803,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="41" t="s">
         <v>40</v>
       </c>
@@ -13823,8 +13821,8 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="86" t="s">
         <v>48</v>
       </c>
@@ -13836,7 +13834,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="17" x14ac:dyDescent="0.2">
       <c r="B11" s="69" t="s">
         <v>50</v>
       </c>
@@ -13851,7 +13849,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" ht="34" x14ac:dyDescent="0.2">
       <c r="B12" s="70" t="s">
         <v>51</v>
       </c>
@@ -13866,7 +13864,7 @@
         <v>204.00139677991956</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="66" t="s">
         <v>52</v>
       </c>
@@ -13881,7 +13879,7 @@
         <v>136.05430177391423</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F14" s="4">
         <v>3</v>
       </c>
@@ -13890,7 +13888,7 @@
         <v>112.49899248137271</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F15" s="4">
         <v>4</v>
       </c>
@@ -13899,7 +13897,7 @@
         <v>104.33304225468159</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F16" s="4">
         <v>5</v>
       </c>
@@ -13908,7 +13906,7 @@
         <v>101.50214148931099</v>
       </c>
     </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F17" s="4">
         <v>6</v>
       </c>
@@ -13917,7 +13915,7 @@
         <v>100.52074937683138</v>
       </c>
     </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F18" s="4">
         <v>7</v>
       </c>
@@ -13926,7 +13924,7 @@
         <v>100.18052887520912</v>
       </c>
     </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F19" s="4">
         <v>8</v>
       </c>
@@ -13935,7 +13933,7 @@
         <v>100.06258418393618</v>
       </c>
     </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F20" s="4">
         <v>9</v>
       </c>
@@ -13944,7 +13942,7 @@
         <v>100.02169614181898</v>
       </c>
     </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F21" s="4">
         <v>10</v>
       </c>
@@ -13953,7 +13951,7 @@
         <v>100.00752143017969</v>
       </c>
     </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F22" s="4">
         <v>11</v>
       </c>
@@ -13962,7 +13960,7 @@
         <v>100.00260746414824</v>
       </c>
     </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F23" s="4">
         <v>12</v>
       </c>
@@ -13971,7 +13969,7 @@
         <v>100.0009039330449</v>
       </c>
     </row>
-    <row r="24" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F24" s="4">
         <v>13</v>
       </c>
@@ -13980,7 +13978,7 @@
         <v>100.00031336766422</v>
       </c>
     </row>
-    <row r="25" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F25" s="4">
         <v>14</v>
       </c>
@@ -13989,7 +13987,7 @@
         <v>100.00010863558262</v>
       </c>
     </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F26" s="4">
         <v>15</v>
       </c>
@@ -13998,7 +13996,7 @@
         <v>100.0000376608411</v>
       </c>
     </row>
-    <row r="27" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F27" s="4">
         <v>16</v>
       </c>
@@ -14007,7 +14005,7 @@
         <v>100.00001305593359</v>
       </c>
     </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F28" s="4">
         <v>17</v>
       </c>
@@ -14016,7 +14014,7 @@
         <v>100.00000452611776</v>
       </c>
     </row>
-    <row r="29" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F29" s="4">
         <v>18</v>
       </c>
@@ -14025,7 +14023,7 @@
         <v>100.00000156907524</v>
       </c>
     </row>
-    <row r="30" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F30" s="4">
         <v>19</v>
       </c>
@@ -14034,7 +14032,7 @@
         <v>100.00000054395339</v>
       </c>
     </row>
-    <row r="31" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F31" s="4">
         <v>20</v>
       </c>
@@ -14043,7 +14041,7 @@
         <v>100.00000018857304</v>
       </c>
     </row>
-    <row r="32" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F32" s="4">
         <v>21</v>
       </c>
@@ -14052,7 +14050,7 @@
         <v>100.00000006537286</v>
       </c>
     </row>
-    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F33" s="4">
         <v>22</v>
       </c>
@@ -14061,7 +14059,7 @@
         <v>100.0000000226629</v>
       </c>
     </row>
-    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F34" s="4">
         <v>23</v>
       </c>
@@ -14070,7 +14068,7 @@
         <v>100.00000000785657</v>
       </c>
     </row>
-    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F35" s="4">
         <v>24</v>
       </c>
@@ -14079,7 +14077,7 @@
         <v>100.00000000272365</v>
       </c>
     </row>
-    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F36" s="4">
         <v>25</v>
       </c>
@@ -14088,7 +14086,7 @@
         <v>100.00000000094421</v>
       </c>
     </row>
-    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F37" s="4">
         <v>26</v>
       </c>
@@ -14097,7 +14095,7 @@
         <v>100.00000000032733</v>
       </c>
     </row>
-    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F38" s="4">
         <v>27</v>
       </c>
@@ -14106,7 +14104,7 @@
         <v>100.00000000011347</v>
       </c>
     </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F39" s="4">
         <v>28</v>
       </c>
@@ -14115,7 +14113,7 @@
         <v>100.00000000003934</v>
       </c>
     </row>
-    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F40" s="4">
         <v>29</v>
       </c>
@@ -14124,7 +14122,7 @@
         <v>100.00000000001364</v>
       </c>
     </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F41" s="4">
         <v>30</v>
       </c>
@@ -14133,7 +14131,7 @@
         <v>100.00000000000473</v>
       </c>
     </row>
-    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F42" s="4">
         <v>31</v>
       </c>
@@ -14142,7 +14140,7 @@
         <v>100.00000000000163</v>
       </c>
     </row>
-    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F43" s="4">
         <v>32</v>
       </c>
@@ -14151,7 +14149,7 @@
         <v>100.00000000000057</v>
       </c>
     </row>
-    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F44" s="4">
         <v>33</v>
       </c>
@@ -14160,7 +14158,7 @@
         <v>100.0000000000002</v>
       </c>
     </row>
-    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F45" s="4">
         <v>34</v>
       </c>
@@ -14169,7 +14167,7 @@
         <v>100.00000000000007</v>
       </c>
     </row>
-    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F46" s="4">
         <v>35</v>
       </c>
@@ -14178,7 +14176,7 @@
         <v>100.00000000000003</v>
       </c>
     </row>
-    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F47" s="4">
         <v>36</v>
       </c>
@@ -14187,7 +14185,7 @@
         <v>100.00000000000001</v>
       </c>
     </row>
-    <row r="48" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F48" s="4">
         <v>37</v>
       </c>
@@ -14196,7 +14194,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F49" s="4">
         <v>38</v>
       </c>
@@ -14205,7 +14203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F50" s="4">
         <v>39</v>
       </c>
@@ -14214,7 +14212,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F51" s="4">
         <v>40</v>
       </c>
@@ -14223,7 +14221,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F52" s="4">
         <v>41</v>
       </c>
@@ -14232,7 +14230,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F53" s="4">
         <v>42</v>
       </c>
@@ -14241,7 +14239,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F54" s="4">
         <v>43</v>
       </c>
@@ -14250,7 +14248,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F55" s="4">
         <v>44</v>
       </c>
@@ -14259,7 +14257,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F56" s="4">
         <v>45</v>
       </c>
@@ -14268,7 +14266,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F57" s="4">
         <v>46</v>
       </c>
@@ -14277,7 +14275,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F58" s="4">
         <v>47</v>
       </c>
@@ -14286,7 +14284,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F59" s="4">
         <v>48</v>
       </c>
@@ -14295,7 +14293,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F60" s="4">
         <v>49</v>
       </c>
@@ -14304,7 +14302,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F61" s="4">
         <v>50</v>
       </c>
@@ -14313,7 +14311,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F62" s="4">
         <v>51</v>
       </c>
@@ -14322,7 +14320,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F63" s="4">
         <v>52</v>
       </c>
@@ -14331,7 +14329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F64" s="4">
         <v>53</v>
       </c>
@@ -14340,7 +14338,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F65" s="4">
         <v>54</v>
       </c>
@@ -14349,7 +14347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F66" s="4">
         <v>55</v>
       </c>
@@ -14358,7 +14356,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F67" s="4">
         <v>56</v>
       </c>
@@ -14367,7 +14365,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F68" s="4">
         <v>57</v>
       </c>
@@ -14376,7 +14374,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F69" s="4">
         <v>58</v>
       </c>
@@ -14385,7 +14383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F70" s="4">
         <v>59</v>
       </c>
@@ -14394,7 +14392,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F71" s="4">
         <v>60</v>
       </c>
@@ -14403,7 +14401,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F72" s="4">
         <v>61</v>
       </c>
@@ -14412,7 +14410,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F73" s="4">
         <v>62</v>
       </c>
@@ -14421,7 +14419,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F74" s="4">
         <v>63</v>
       </c>
@@ -14430,7 +14428,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F75" s="4">
         <v>64</v>
       </c>
@@ -14439,7 +14437,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F76" s="4">
         <v>65</v>
       </c>
@@ -14448,7 +14446,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F77" s="4">
         <v>66</v>
       </c>
@@ -14457,7 +14455,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F78" s="4">
         <v>67</v>
       </c>
@@ -14466,7 +14464,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="79" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F79" s="4">
         <v>68</v>
       </c>
@@ -14475,7 +14473,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F80" s="4">
         <v>69</v>
       </c>
@@ -14484,7 +14482,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F81" s="4">
         <v>70</v>
       </c>
@@ -14493,7 +14491,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F82" s="4">
         <v>71</v>
       </c>
@@ -14502,7 +14500,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F83" s="4">
         <v>72</v>
       </c>
@@ -14511,7 +14509,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F84" s="4">
         <v>73</v>
       </c>
@@ -14520,7 +14518,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F85" s="4">
         <v>74</v>
       </c>
@@ -14529,7 +14527,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F86" s="4">
         <v>75</v>
       </c>
@@ -14538,7 +14536,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F87" s="4">
         <v>76</v>
       </c>
@@ -14547,7 +14545,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F88" s="4">
         <v>77</v>
       </c>
@@ -14556,7 +14554,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F89" s="4">
         <v>78</v>
       </c>
@@ -14565,7 +14563,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F90" s="4">
         <v>79</v>
       </c>
@@ -14574,7 +14572,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F91" s="4">
         <v>80</v>
       </c>
@@ -14583,7 +14581,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F92" s="4">
         <v>81</v>
       </c>
@@ -14592,7 +14590,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F93" s="4">
         <v>82</v>
       </c>
@@ -14601,7 +14599,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F94" s="4">
         <v>83</v>
       </c>
@@ -14610,7 +14608,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F95" s="4">
         <v>84</v>
       </c>
@@ -14619,7 +14617,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F96" s="4">
         <v>85</v>
       </c>
@@ -14628,7 +14626,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F97" s="4">
         <v>86</v>
       </c>
@@ -14637,7 +14635,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F98" s="4">
         <v>87</v>
       </c>
@@ -14646,7 +14644,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F99" s="4">
         <v>88</v>
       </c>
@@ -14655,7 +14653,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="100" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F100" s="4">
         <v>89</v>
       </c>
@@ -14664,7 +14662,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F101" s="4">
         <v>90</v>
       </c>
@@ -14673,7 +14671,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F102" s="4">
         <v>91</v>
       </c>
@@ -14682,7 +14680,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F103" s="4">
         <v>92</v>
       </c>
@@ -14691,7 +14689,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F104" s="4">
         <v>93</v>
       </c>
@@ -14700,7 +14698,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F105" s="4">
         <v>94</v>
       </c>
@@ -14709,7 +14707,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F106" s="4">
         <v>95</v>
       </c>
@@ -14718,7 +14716,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F107" s="4">
         <v>96</v>
       </c>
@@ -14727,7 +14725,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="108" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F108" s="4">
         <v>97</v>
       </c>
@@ -14736,7 +14734,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F109" s="4">
         <v>98</v>
       </c>
@@ -14745,7 +14743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F110" s="4">
         <v>99</v>
       </c>
@@ -14754,7 +14752,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="111" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F111" s="4">
         <v>100</v>
       </c>
@@ -14763,7 +14761,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F112" s="4">
         <v>101</v>
       </c>
@@ -14772,7 +14770,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="113" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F113" s="4">
         <v>102</v>
       </c>
@@ -14781,7 +14779,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="114" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F114" s="4">
         <v>103</v>
       </c>
@@ -14790,7 +14788,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F115" s="4">
         <v>104</v>
       </c>
@@ -14799,7 +14797,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F116" s="4">
         <v>105</v>
       </c>
@@ -14808,7 +14806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="117" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F117" s="4">
         <v>106</v>
       </c>
@@ -14817,7 +14815,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="118" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F118" s="4">
         <v>107</v>
       </c>
@@ -14826,7 +14824,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F119" s="4">
         <v>108</v>
       </c>
@@ -14835,7 +14833,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="120" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F120" s="4">
         <v>109</v>
       </c>
@@ -14844,7 +14842,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="121" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F121" s="4">
         <v>110</v>
       </c>
@@ -14853,7 +14851,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="122" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F122" s="4">
         <v>111</v>
       </c>
@@ -14862,7 +14860,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="123" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F123" s="4">
         <v>112</v>
       </c>
@@ -14871,7 +14869,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F124" s="4">
         <v>113</v>
       </c>
@@ -14880,7 +14878,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="125" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F125" s="4">
         <v>114</v>
       </c>
@@ -14889,7 +14887,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="126" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F126" s="4">
         <v>115</v>
       </c>
@@ -14898,7 +14896,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="127" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F127" s="4">
         <v>116</v>
       </c>
@@ -14907,7 +14905,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F128" s="4">
         <v>117</v>
       </c>
@@ -14916,7 +14914,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="129" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F129" s="4">
         <v>118</v>
       </c>
@@ -14925,7 +14923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="130" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F130" s="4">
         <v>119</v>
       </c>
@@ -14934,7 +14932,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F131" s="4">
         <v>120</v>
       </c>
@@ -14943,7 +14941,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="132" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F132" s="4">
         <v>121</v>
       </c>
@@ -14952,7 +14950,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F133" s="4">
         <v>122</v>
       </c>
@@ -14961,7 +14959,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F134" s="4">
         <v>123</v>
       </c>
@@ -14970,7 +14968,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F135" s="4">
         <v>124</v>
       </c>
@@ -14979,7 +14977,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F136" s="4">
         <v>125</v>
       </c>
@@ -14988,7 +14986,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F137" s="4">
         <v>126</v>
       </c>
@@ -14997,7 +14995,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F138" s="4">
         <v>127</v>
       </c>
@@ -15006,7 +15004,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F139" s="4">
         <v>128</v>
       </c>
@@ -15015,7 +15013,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F140" s="4">
         <v>129</v>
       </c>
@@ -15024,7 +15022,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F141" s="4">
         <v>130</v>
       </c>
@@ -15033,7 +15031,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F142" s="4">
         <v>131</v>
       </c>
@@ -15042,7 +15040,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F143" s="4">
         <v>132</v>
       </c>
@@ -15051,7 +15049,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F144" s="4">
         <v>133</v>
       </c>
@@ -15060,7 +15058,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F145" s="4">
         <v>134</v>
       </c>
@@ -15069,7 +15067,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F146" s="4">
         <v>135</v>
       </c>
@@ -15078,7 +15076,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F147" s="4">
         <v>136</v>
       </c>
@@ -15087,7 +15085,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F148" s="4">
         <v>137</v>
       </c>
@@ -15096,7 +15094,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="149" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F149" s="4">
         <v>138</v>
       </c>
@@ -15105,7 +15103,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F150" s="4">
         <v>139</v>
       </c>
@@ -15114,7 +15112,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F151" s="4">
         <v>140</v>
       </c>
@@ -15123,7 +15121,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="152" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F152" s="4">
         <v>141</v>
       </c>
@@ -15132,7 +15130,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="153" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F153" s="4">
         <v>142</v>
       </c>
@@ -15141,7 +15139,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F154" s="4">
         <v>143</v>
       </c>
@@ -15150,7 +15148,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F155" s="4">
         <v>144</v>
       </c>
@@ -15159,7 +15157,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="156" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F156" s="4">
         <v>145</v>
       </c>
@@ -15168,7 +15166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="157" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F157" s="4">
         <v>146</v>
       </c>
@@ -15177,7 +15175,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="158" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F158" s="4">
         <v>147</v>
       </c>
@@ -15186,7 +15184,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="159" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F159" s="4">
         <v>148</v>
       </c>
@@ -15195,7 +15193,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="160" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F160" s="4">
         <v>149</v>
       </c>
@@ -15204,7 +15202,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="161" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F161" s="4">
         <v>150</v>
       </c>
@@ -15213,7 +15211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="162" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F162" s="4">
         <v>151</v>
       </c>
@@ -15222,7 +15220,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="163" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F163" s="4">
         <v>152</v>
       </c>
@@ -15231,7 +15229,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="164" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F164" s="4">
         <v>153</v>
       </c>
@@ -15240,7 +15238,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="165" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F165" s="4">
         <v>154</v>
       </c>
@@ -15249,7 +15247,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F166" s="4">
         <v>155</v>
       </c>
@@ -15258,7 +15256,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F167" s="4">
         <v>156</v>
       </c>
@@ -15267,7 +15265,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="168" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F168" s="4">
         <v>157</v>
       </c>
@@ -15276,7 +15274,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="169" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F169" s="4">
         <v>158</v>
       </c>
@@ -15285,7 +15283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F170" s="4">
         <v>159</v>
       </c>
@@ -15294,7 +15292,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="171" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F171" s="4">
         <v>160</v>
       </c>
@@ -15303,7 +15301,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F172" s="4">
         <v>161</v>
       </c>
@@ -15312,7 +15310,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F173" s="4">
         <v>162</v>
       </c>
@@ -15321,7 +15319,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="174" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F174" s="4">
         <v>163</v>
       </c>
@@ -15330,7 +15328,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F175" s="4">
         <v>164</v>
       </c>
@@ -15339,7 +15337,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="176" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F176" s="4">
         <v>165</v>
       </c>
@@ -15348,7 +15346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="177" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F177" s="4">
         <v>166</v>
       </c>
@@ -15357,7 +15355,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="178" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F178" s="4">
         <v>167</v>
       </c>
@@ -15366,7 +15364,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F179" s="4">
         <v>168</v>
       </c>
@@ -15375,7 +15373,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="180" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F180" s="4">
         <v>169</v>
       </c>
@@ -15384,7 +15382,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="181" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F181" s="4">
         <v>170</v>
       </c>
@@ -15393,7 +15391,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="182" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F182" s="4">
         <v>171</v>
       </c>
@@ -15402,7 +15400,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="183" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F183" s="4">
         <v>172</v>
       </c>
@@ -15411,7 +15409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F184" s="4">
         <v>173</v>
       </c>
@@ -15420,7 +15418,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="185" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F185" s="4">
         <v>174</v>
       </c>
@@ -15429,7 +15427,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="186" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F186" s="4">
         <v>175</v>
       </c>
@@ -15438,7 +15436,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F187" s="4">
         <v>176</v>
       </c>
@@ -15447,7 +15445,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="188" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F188" s="4">
         <v>177</v>
       </c>
@@ -15456,7 +15454,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F189" s="4">
         <v>178</v>
       </c>
@@ -15465,7 +15463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="190" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F190" s="4">
         <v>179</v>
       </c>
@@ -15474,7 +15472,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="191" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F191" s="4">
         <v>180</v>
       </c>
@@ -15483,7 +15481,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="192" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F192" s="4">
         <v>181</v>
       </c>
@@ -15492,7 +15490,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="193" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F193" s="4">
         <v>182</v>
       </c>
@@ -15501,7 +15499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="194" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F194" s="4">
         <v>183</v>
       </c>
@@ -15510,7 +15508,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="195" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F195" s="4">
         <v>184</v>
       </c>
@@ -15519,7 +15517,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="196" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F196" s="4">
         <v>185</v>
       </c>
@@ -15528,7 +15526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="197" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F197" s="4">
         <v>186</v>
       </c>
@@ -15537,7 +15535,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="198" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F198" s="4">
         <v>187</v>
       </c>
@@ -15546,7 +15544,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="199" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F199" s="4">
         <v>188</v>
       </c>
@@ -15555,7 +15553,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F200" s="4">
         <v>189</v>
       </c>
@@ -15564,7 +15562,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="201" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F201" s="4">
         <v>190</v>
       </c>
@@ -15573,7 +15571,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F202" s="4">
         <v>191</v>
       </c>
@@ -15582,7 +15580,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F203" s="4">
         <v>192</v>
       </c>
@@ -15591,7 +15589,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="204" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F204" s="4">
         <v>193</v>
       </c>
@@ -15600,7 +15598,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="205" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F205" s="4">
         <v>194</v>
       </c>
@@ -15609,7 +15607,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="206" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F206" s="4">
         <v>195</v>
       </c>
@@ -15618,7 +15616,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="207" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F207" s="4">
         <v>196</v>
       </c>
@@ -15627,7 +15625,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="208" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F208" s="4">
         <v>197</v>
       </c>
@@ -15636,7 +15634,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="209" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F209" s="4">
         <v>198</v>
       </c>
@@ -15645,7 +15643,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="210" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F210" s="4">
         <v>199</v>
       </c>
@@ -15654,7 +15652,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="211" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F211" s="4">
         <v>200</v>
       </c>
@@ -15663,7 +15661,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="212" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F212" s="4">
         <v>201</v>
       </c>
@@ -15672,7 +15670,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="213" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F213" s="4">
         <v>202</v>
       </c>
@@ -15681,7 +15679,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F214" s="4">
         <v>203</v>
       </c>
@@ -15690,7 +15688,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F215" s="4">
         <v>204</v>
       </c>
@@ -15699,7 +15697,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F216" s="4">
         <v>205</v>
       </c>
@@ -15708,7 +15706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F217" s="4">
         <v>206</v>
       </c>
@@ -15717,7 +15715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="218" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F218" s="4">
         <v>207</v>
       </c>
@@ -15726,7 +15724,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="219" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F219" s="4">
         <v>208</v>
       </c>
@@ -15735,7 +15733,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="220" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F220" s="4">
         <v>209</v>
       </c>
@@ -15744,7 +15742,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F221" s="4">
         <v>210</v>
       </c>
@@ -15753,7 +15751,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="222" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F222" s="4">
         <v>211</v>
       </c>
@@ -15762,7 +15760,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="223" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F223" s="4">
         <v>212</v>
       </c>
@@ -15771,7 +15769,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="224" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F224" s="4">
         <v>213</v>
       </c>
@@ -15780,7 +15778,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="225" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F225" s="4">
         <v>214</v>
       </c>
@@ -15789,7 +15787,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="226" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F226" s="4">
         <v>215</v>
       </c>
@@ -15798,7 +15796,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="227" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F227" s="4">
         <v>216</v>
       </c>
@@ -15807,7 +15805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="228" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F228" s="4">
         <v>217</v>
       </c>
@@ -15816,7 +15814,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="229" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F229" s="4">
         <v>218</v>
       </c>
@@ -15825,7 +15823,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F230" s="4">
         <v>219</v>
       </c>
@@ -15834,7 +15832,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="231" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F231" s="4">
         <v>220</v>
       </c>
@@ -15843,7 +15841,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="232" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F232" s="4">
         <v>221</v>
       </c>
@@ -15852,7 +15850,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="233" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F233" s="4">
         <v>222</v>
       </c>
@@ -15861,7 +15859,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="234" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F234" s="4">
         <v>223</v>
       </c>
@@ -15870,7 +15868,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="235" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F235" s="4">
         <v>224</v>
       </c>
@@ -15879,7 +15877,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="236" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F236" s="4">
         <v>225</v>
       </c>
@@ -15888,7 +15886,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F237" s="4">
         <v>226</v>
       </c>
@@ -15897,7 +15895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="238" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F238" s="4">
         <v>227</v>
       </c>
@@ -15906,7 +15904,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="239" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F239" s="4">
         <v>228</v>
       </c>
@@ -15915,7 +15913,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="240" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F240" s="4">
         <v>229</v>
       </c>
@@ -15924,7 +15922,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="241" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F241" s="4">
         <v>230</v>
       </c>
@@ -15933,7 +15931,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="242" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F242" s="4">
         <v>231</v>
       </c>
@@ -15942,7 +15940,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="243" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F243" s="4">
         <v>232</v>
       </c>
@@ -15951,7 +15949,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="244" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F244" s="4">
         <v>233</v>
       </c>
@@ -15960,7 +15958,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="245" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F245" s="4">
         <v>234</v>
       </c>
@@ -15969,7 +15967,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="246" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F246" s="4">
         <v>235</v>
       </c>
@@ -15978,7 +15976,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F247" s="4">
         <v>236</v>
       </c>
@@ -15987,7 +15985,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F248" s="4">
         <v>237</v>
       </c>
@@ -15996,7 +15994,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="249" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F249" s="4">
         <v>238</v>
       </c>
@@ -16005,7 +16003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="250" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F250" s="4">
         <v>239</v>
       </c>
@@ -16014,7 +16012,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F251" s="4">
         <v>240</v>
       </c>
@@ -16023,7 +16021,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="252" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F252" s="4">
         <v>241</v>
       </c>
@@ -16032,7 +16030,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="253" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F253" s="4">
         <v>242</v>
       </c>
@@ -16041,7 +16039,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="254" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F254" s="4">
         <v>243</v>
       </c>
@@ -16050,7 +16048,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="255" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F255" s="4">
         <v>244</v>
       </c>
@@ -16059,7 +16057,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F256" s="4">
         <v>245</v>
       </c>
@@ -16068,7 +16066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="257" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F257" s="4">
         <v>246</v>
       </c>
@@ -16077,7 +16075,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="258" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F258" s="4">
         <v>247</v>
       </c>
@@ -16086,7 +16084,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="259" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F259" s="4">
         <v>248</v>
       </c>
@@ -16095,7 +16093,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F260" s="4">
         <v>249</v>
       </c>
@@ -16104,7 +16102,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="261" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F261" s="4">
         <v>250</v>
       </c>
@@ -16113,7 +16111,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="262" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F262" s="4">
         <v>251</v>
       </c>
@@ -16122,7 +16120,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="263" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F263" s="4">
         <v>252</v>
       </c>
@@ -16131,7 +16129,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="264" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F264" s="4">
         <v>253</v>
       </c>
@@ -16140,7 +16138,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="265" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F265" s="4">
         <v>254</v>
       </c>
@@ -16149,7 +16147,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F266" s="4">
         <v>255</v>
       </c>
@@ -16158,7 +16156,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="267" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F267" s="4">
         <v>256</v>
       </c>
@@ -16167,7 +16165,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F268" s="4">
         <v>257</v>
       </c>
@@ -16176,7 +16174,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="269" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F269" s="4">
         <v>258</v>
       </c>
@@ -16185,7 +16183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="270" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F270" s="4">
         <v>259</v>
       </c>
@@ -16194,7 +16192,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="271" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F271" s="4">
         <v>260</v>
       </c>
@@ -16203,7 +16201,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="272" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F272" s="4">
         <v>261</v>
       </c>
@@ -16212,7 +16210,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="273" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F273" s="4">
         <v>262</v>
       </c>
@@ -16221,7 +16219,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="274" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F274" s="4">
         <v>263</v>
       </c>
@@ -16230,7 +16228,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="275" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F275" s="4">
         <v>264</v>
       </c>
@@ -16239,7 +16237,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="276" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F276" s="4">
         <v>265</v>
       </c>
@@ -16248,7 +16246,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="277" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F277" s="4">
         <v>266</v>
       </c>
@@ -16257,7 +16255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="278" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F278" s="4">
         <v>267</v>
       </c>
@@ -16266,7 +16264,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="279" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F279" s="4">
         <v>268</v>
       </c>
@@ -16275,7 +16273,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="280" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F280" s="4">
         <v>269</v>
       </c>
@@ -16284,7 +16282,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="281" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F281" s="4">
         <v>270</v>
       </c>
@@ -16293,7 +16291,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="282" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F282" s="4">
         <v>271</v>
       </c>
@@ -16302,7 +16300,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="283" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F283" s="4">
         <v>272</v>
       </c>
@@ -16311,7 +16309,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="284" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F284" s="4">
         <v>273</v>
       </c>
@@ -16320,7 +16318,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="285" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F285" s="4">
         <v>274</v>
       </c>
@@ -16329,7 +16327,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="286" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F286" s="4">
         <v>275</v>
       </c>
@@ -16338,7 +16336,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="287" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F287" s="4">
         <v>276</v>
       </c>
@@ -16347,7 +16345,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="288" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F288" s="4">
         <v>277</v>
       </c>
@@ -16356,7 +16354,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="289" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F289" s="4">
         <v>278</v>
       </c>
@@ -16365,7 +16363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="290" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F290" s="4">
         <v>279</v>
       </c>
@@ -16374,7 +16372,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="291" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F291" s="4">
         <v>280</v>
       </c>
@@ -16383,7 +16381,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="292" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F292" s="4">
         <v>281</v>
       </c>
@@ -16392,7 +16390,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="293" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F293" s="4">
         <v>282</v>
       </c>
@@ -16401,7 +16399,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="294" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F294" s="4">
         <v>283</v>
       </c>
@@ -16410,7 +16408,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="295" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F295" s="4">
         <v>284</v>
       </c>
@@ -16419,7 +16417,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="296" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F296" s="4">
         <v>285</v>
       </c>
@@ -16428,7 +16426,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="297" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F297" s="4">
         <v>286</v>
       </c>
@@ -16437,7 +16435,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="298" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F298" s="4">
         <v>287</v>
       </c>
@@ -16446,7 +16444,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="299" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F299" s="4">
         <v>288</v>
       </c>
@@ -16455,7 +16453,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="300" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F300" s="4">
         <v>289</v>
       </c>
@@ -16464,7 +16462,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="301" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F301" s="4">
         <v>290</v>
       </c>
@@ -16473,7 +16471,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="302" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F302" s="4">
         <v>291</v>
       </c>
@@ -16482,7 +16480,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="303" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F303" s="4">
         <v>292</v>
       </c>
@@ -16491,7 +16489,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="304" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F304" s="4">
         <v>293</v>
       </c>
@@ -16500,7 +16498,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="305" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F305" s="4">
         <v>294</v>
       </c>
@@ -16509,7 +16507,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="306" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F306" s="4">
         <v>295</v>
       </c>
@@ -16518,7 +16516,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="307" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F307" s="4">
         <v>296</v>
       </c>
@@ -16527,7 +16525,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="308" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F308" s="4">
         <v>297</v>
       </c>
@@ -16536,7 +16534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="309" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F309" s="4">
         <v>298</v>
       </c>
@@ -16545,7 +16543,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="310" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F310" s="4">
         <v>299</v>
       </c>
@@ -16554,7 +16552,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="311" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F311" s="4">
         <v>300</v>
       </c>
@@ -16563,7 +16561,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="312" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F312" s="4">
         <v>301</v>
       </c>
@@ -16572,7 +16570,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="313" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F313" s="4">
         <v>302</v>
       </c>
@@ -16581,7 +16579,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F314" s="4">
         <v>303</v>
       </c>
@@ -16590,7 +16588,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="315" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F315" s="4">
         <v>304</v>
       </c>
@@ -16599,7 +16597,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="316" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F316" s="4">
         <v>305</v>
       </c>
@@ -16608,7 +16606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="317" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F317" s="4">
         <v>306</v>
       </c>
@@ -16617,7 +16615,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="318" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F318" s="4">
         <v>307</v>
       </c>
@@ -16626,7 +16624,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="319" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F319" s="4">
         <v>308</v>
       </c>
@@ -16635,7 +16633,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="320" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F320" s="4">
         <v>309</v>
       </c>
@@ -16644,7 +16642,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="321" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F321" s="4">
         <v>310</v>
       </c>
@@ -16653,7 +16651,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="322" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F322" s="4">
         <v>311</v>
       </c>
@@ -16662,7 +16660,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="323" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F323" s="4">
         <v>312</v>
       </c>
@@ -16671,7 +16669,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="324" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F324" s="4">
         <v>313</v>
       </c>
@@ -16680,7 +16678,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="325" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F325" s="4">
         <v>314</v>
       </c>
@@ -16689,7 +16687,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="326" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F326" s="4">
         <v>315</v>
       </c>
@@ -16698,7 +16696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="327" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F327" s="4">
         <v>316</v>
       </c>
@@ -16707,7 +16705,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="328" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F328" s="4">
         <v>317</v>
       </c>
@@ -16716,7 +16714,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="329" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F329" s="4">
         <v>318</v>
       </c>
@@ -16725,7 +16723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="330" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F330" s="4">
         <v>319</v>
       </c>
@@ -16734,7 +16732,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="331" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F331" s="4">
         <v>320</v>
       </c>
@@ -16743,7 +16741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="332" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F332" s="4">
         <v>321</v>
       </c>
@@ -16752,7 +16750,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="333" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F333" s="4">
         <v>322</v>
       </c>
@@ -16761,7 +16759,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="334" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F334" s="4">
         <v>323</v>
       </c>
@@ -16770,7 +16768,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="335" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F335" s="4">
         <v>324</v>
       </c>
@@ -16779,7 +16777,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="336" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F336" s="4">
         <v>325</v>
       </c>
@@ -16788,7 +16786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="337" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F337" s="4">
         <v>326</v>
       </c>
@@ -16797,7 +16795,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="338" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F338" s="4">
         <v>327</v>
       </c>
@@ -16806,7 +16804,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="339" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F339" s="4">
         <v>328</v>
       </c>
@@ -16815,7 +16813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="340" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F340" s="4">
         <v>329</v>
       </c>
@@ -16824,7 +16822,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="341" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F341" s="4">
         <v>330</v>
       </c>
@@ -16833,7 +16831,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="342" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F342" s="4">
         <v>331</v>
       </c>
@@ -16842,7 +16840,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="343" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F343" s="4">
         <v>332</v>
       </c>
@@ -16851,7 +16849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="344" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F344" s="4">
         <v>333</v>
       </c>
@@ -16860,7 +16858,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="345" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F345" s="4">
         <v>334</v>
       </c>
@@ -16869,7 +16867,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="346" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F346" s="4">
         <v>335</v>
       </c>
@@ -16878,7 +16876,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="347" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F347" s="4">
         <v>336</v>
       </c>
@@ -16887,7 +16885,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="348" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F348" s="4">
         <v>337</v>
       </c>
@@ -16896,7 +16894,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="349" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F349" s="4">
         <v>338</v>
       </c>
@@ -16905,7 +16903,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="350" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F350" s="4">
         <v>339</v>
       </c>
@@ -16914,7 +16912,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="351" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F351" s="4">
         <v>340</v>
       </c>
@@ -16923,7 +16921,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="352" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F352" s="4">
         <v>341</v>
       </c>
@@ -16932,7 +16930,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="353" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F353" s="4">
         <v>342</v>
       </c>
@@ -16941,7 +16939,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="354" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F354" s="4">
         <v>343</v>
       </c>
@@ -16950,7 +16948,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="355" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F355" s="4">
         <v>344</v>
       </c>
@@ -16959,7 +16957,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="356" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F356" s="4">
         <v>345</v>
       </c>
@@ -16968,7 +16966,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="357" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F357" s="4">
         <v>346</v>
       </c>
@@ -16977,7 +16975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="358" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F358" s="4">
         <v>347</v>
       </c>
@@ -16986,7 +16984,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="359" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F359" s="4">
         <v>348</v>
       </c>
@@ -16995,7 +16993,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="360" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F360" s="4">
         <v>349</v>
       </c>
@@ -17004,7 +17002,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="361" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F361" s="4">
         <v>350</v>
       </c>
@@ -17013,7 +17011,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="362" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F362" s="4">
         <v>351</v>
       </c>
@@ -17022,7 +17020,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="363" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F363" s="4">
         <v>352</v>
       </c>
@@ -17031,7 +17029,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="364" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F364" s="4">
         <v>353</v>
       </c>
@@ -17040,7 +17038,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="365" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F365" s="4">
         <v>354</v>
       </c>
@@ -17049,7 +17047,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="366" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F366" s="4">
         <v>355</v>
       </c>
@@ -17058,7 +17056,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="367" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F367" s="4">
         <v>356</v>
       </c>
@@ -17067,7 +17065,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="368" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F368" s="4">
         <v>357</v>
       </c>
@@ -17076,7 +17074,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="369" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F369" s="4">
         <v>358</v>
       </c>
@@ -17085,7 +17083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="370" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F370" s="4">
         <v>359</v>
       </c>
@@ -17094,7 +17092,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="371" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F371" s="4">
         <v>360</v>
       </c>
@@ -17103,7 +17101,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="372" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F372" s="4">
         <v>361</v>
       </c>
@@ -17112,7 +17110,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="373" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F373" s="4">
         <v>362</v>
       </c>
@@ -17121,7 +17119,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="374" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F374" s="4">
         <v>363</v>
       </c>
@@ -17130,7 +17128,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="375" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F375" s="4">
         <v>364</v>
       </c>
@@ -17139,7 +17137,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="376" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F376" s="4">
         <v>365</v>
       </c>
@@ -17148,7 +17146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="377" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F377" s="4">
         <v>366</v>
       </c>
@@ -17157,7 +17155,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="378" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F378" s="4">
         <v>367</v>
       </c>
@@ -17166,7 +17164,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="379" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F379" s="4">
         <v>368</v>
       </c>
@@ -17175,7 +17173,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="380" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F380" s="4">
         <v>369</v>
       </c>
@@ -17184,7 +17182,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="381" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F381" s="4">
         <v>370</v>
       </c>
@@ -17193,7 +17191,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="382" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F382" s="4">
         <v>371</v>
       </c>
@@ -17202,7 +17200,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="383" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F383" s="4">
         <v>372</v>
       </c>
@@ -17211,7 +17209,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="384" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F384" s="4">
         <v>373</v>
       </c>
@@ -17220,7 +17218,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="385" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F385" s="4">
         <v>374</v>
       </c>
@@ -17229,7 +17227,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="386" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F386" s="4">
         <v>375</v>
       </c>
@@ -17238,7 +17236,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="387" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F387" s="4">
         <v>376</v>
       </c>
@@ -17247,7 +17245,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="388" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F388" s="4">
         <v>377</v>
       </c>
@@ -17256,7 +17254,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="389" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F389" s="4">
         <v>378</v>
       </c>
@@ -17265,7 +17263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="390" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F390" s="4">
         <v>379</v>
       </c>
@@ -17274,7 +17272,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="391" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F391" s="4">
         <v>380</v>
       </c>
@@ -17283,7 +17281,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="392" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F392" s="4">
         <v>381</v>
       </c>
@@ -17292,7 +17290,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="393" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F393" s="4">
         <v>382</v>
       </c>
@@ -17301,7 +17299,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="394" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F394" s="4">
         <v>383</v>
       </c>
@@ -17310,7 +17308,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="395" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F395" s="4">
         <v>384</v>
       </c>
@@ -17319,7 +17317,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="396" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F396" s="4">
         <v>385</v>
       </c>
@@ -17328,7 +17326,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="397" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F397" s="4">
         <v>386</v>
       </c>
@@ -17337,7 +17335,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="398" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F398" s="4">
         <v>387</v>
       </c>
@@ -17346,7 +17344,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="399" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F399" s="4">
         <v>388</v>
       </c>
@@ -17355,7 +17353,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="400" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F400" s="4">
         <v>389</v>
       </c>
@@ -17364,7 +17362,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="401" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F401" s="4">
         <v>390</v>
       </c>
@@ -17373,7 +17371,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="402" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F402" s="4">
         <v>391</v>
       </c>
@@ -17382,7 +17380,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="403" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F403" s="4">
         <v>392</v>
       </c>
@@ -17391,7 +17389,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="404" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F404" s="4">
         <v>393</v>
       </c>
@@ -17400,7 +17398,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="405" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F405" s="4">
         <v>394</v>
       </c>
@@ -17409,7 +17407,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="406" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F406" s="4">
         <v>395</v>
       </c>
@@ -17418,7 +17416,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="407" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F407" s="4">
         <v>396</v>
       </c>
@@ -17427,7 +17425,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="408" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F408" s="4">
         <v>397</v>
       </c>
@@ -17436,7 +17434,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="409" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F409" s="4">
         <v>398</v>
       </c>
@@ -17445,7 +17443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="410" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F410" s="4">
         <v>399</v>
       </c>
@@ -17454,7 +17452,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="411" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F411" s="4">
         <v>400</v>
       </c>
@@ -17463,7 +17461,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="412" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F412" s="4">
         <v>401</v>
       </c>
@@ -17472,7 +17470,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="413" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F413" s="4">
         <v>402</v>
       </c>
@@ -17481,7 +17479,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="414" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F414" s="4">
         <v>403</v>
       </c>
@@ -17490,7 +17488,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="415" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F415" s="4">
         <v>404</v>
       </c>
@@ -17499,7 +17497,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="416" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F416" s="4">
         <v>405</v>
       </c>
@@ -17508,7 +17506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="417" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F417" s="4">
         <v>406</v>
       </c>
@@ -17517,7 +17515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F418" s="4">
         <v>407</v>
       </c>
@@ -17526,7 +17524,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="419" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F419" s="4">
         <v>408</v>
       </c>
@@ -17535,7 +17533,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="420" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F420" s="4">
         <v>409</v>
       </c>
@@ -17544,7 +17542,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="421" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F421" s="4">
         <v>410</v>
       </c>
@@ -17553,7 +17551,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="422" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F422" s="4">
         <v>411</v>
       </c>
@@ -17562,7 +17560,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="423" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F423" s="4">
         <v>412</v>
       </c>
@@ -17571,7 +17569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="424" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F424" s="4">
         <v>413</v>
       </c>
@@ -17580,7 +17578,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="425" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F425" s="4">
         <v>414</v>
       </c>
@@ -17589,7 +17587,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="426" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F426" s="4">
         <v>415</v>
       </c>
@@ -17598,7 +17596,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="427" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F427" s="4">
         <v>416</v>
       </c>
@@ -17607,7 +17605,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="428" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F428" s="4">
         <v>417</v>
       </c>
@@ -17616,7 +17614,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="429" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F429" s="4">
         <v>418</v>
       </c>
@@ -17625,7 +17623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="430" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F430" s="4">
         <v>419</v>
       </c>
@@ -17634,7 +17632,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="431" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F431" s="4">
         <v>420</v>
       </c>
@@ -17643,7 +17641,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="432" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F432" s="4">
         <v>421</v>
       </c>
@@ -17652,7 +17650,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="433" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F433" s="4">
         <v>422</v>
       </c>
@@ -17661,7 +17659,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="434" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F434" s="4">
         <v>423</v>
       </c>
@@ -17670,7 +17668,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="435" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F435" s="4">
         <v>424</v>
       </c>
@@ -17679,7 +17677,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="436" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F436" s="4">
         <v>425</v>
       </c>
@@ -17688,7 +17686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="437" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F437" s="4">
         <v>426</v>
       </c>
@@ -17697,7 +17695,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="438" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F438" s="4">
         <v>427</v>
       </c>
@@ -17706,7 +17704,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="439" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F439" s="4">
         <v>428</v>
       </c>
@@ -17715,7 +17713,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="440" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F440" s="4">
         <v>429</v>
       </c>
@@ -17724,7 +17722,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="441" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F441" s="4">
         <v>430</v>
       </c>
@@ -17733,7 +17731,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="442" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F442" s="4">
         <v>431</v>
       </c>
@@ -17742,7 +17740,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="443" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F443" s="4">
         <v>432</v>
       </c>
@@ -17751,7 +17749,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="444" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F444" s="4">
         <v>433</v>
       </c>
@@ -17760,7 +17758,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="445" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F445" s="4">
         <v>434</v>
       </c>
@@ -17769,7 +17767,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="446" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F446" s="4">
         <v>435</v>
       </c>
@@ -17778,7 +17776,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="447" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F447" s="4">
         <v>436</v>
       </c>
@@ -17787,7 +17785,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="448" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F448" s="4">
         <v>437</v>
       </c>
@@ -17796,7 +17794,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="449" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F449" s="4">
         <v>438</v>
       </c>
@@ -17805,7 +17803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="450" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F450" s="4">
         <v>439</v>
       </c>
@@ -17814,7 +17812,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="451" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F451" s="4">
         <v>440</v>
       </c>
@@ -17823,7 +17821,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="452" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F452" s="4">
         <v>441</v>
       </c>
@@ -17832,7 +17830,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="453" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F453" s="4">
         <v>442</v>
       </c>
@@ -17841,7 +17839,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="454" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F454" s="4">
         <v>443</v>
       </c>
@@ -17850,7 +17848,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="455" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F455" s="4">
         <v>444</v>
       </c>
@@ -17859,7 +17857,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="456" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F456" s="4">
         <v>445</v>
       </c>
@@ -17868,7 +17866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="457" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F457" s="4">
         <v>446</v>
       </c>
@@ -17877,7 +17875,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="458" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F458" s="4">
         <v>447</v>
       </c>
@@ -17886,7 +17884,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="459" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F459" s="4">
         <v>448</v>
       </c>
@@ -17895,7 +17893,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="460" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F460" s="4">
         <v>449</v>
       </c>
@@ -17904,7 +17902,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="461" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F461" s="4">
         <v>450</v>
       </c>
@@ -17913,7 +17911,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="462" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F462" s="4">
         <v>451</v>
       </c>
@@ -17922,7 +17920,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="463" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F463" s="4">
         <v>452</v>
       </c>
@@ -17931,7 +17929,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="464" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F464" s="4">
         <v>453</v>
       </c>
@@ -17940,7 +17938,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="465" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F465" s="4">
         <v>454</v>
       </c>
@@ -17949,7 +17947,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="466" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F466" s="4">
         <v>455</v>
       </c>
@@ -17958,7 +17956,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="467" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F467" s="4">
         <v>456</v>
       </c>
@@ -17967,7 +17965,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="468" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F468" s="4">
         <v>457</v>
       </c>
@@ -17976,7 +17974,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="469" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F469" s="4">
         <v>458</v>
       </c>
@@ -17985,7 +17983,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="470" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F470" s="4">
         <v>459</v>
       </c>
@@ -17994,7 +17992,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="471" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F471" s="4">
         <v>460</v>
       </c>
@@ -18003,7 +18001,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="472" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F472" s="4">
         <v>461</v>
       </c>
@@ -18012,7 +18010,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="473" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F473" s="4">
         <v>462</v>
       </c>
@@ -18021,7 +18019,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="474" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F474" s="4">
         <v>463</v>
       </c>
@@ -18030,7 +18028,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="475" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F475" s="4">
         <v>464</v>
       </c>
@@ -18039,7 +18037,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="476" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F476" s="4">
         <v>465</v>
       </c>
@@ -18048,7 +18046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="477" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F477" s="4">
         <v>466</v>
       </c>
@@ -18057,7 +18055,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="478" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F478" s="4">
         <v>467</v>
       </c>
@@ -18066,7 +18064,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="479" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F479" s="4">
         <v>468</v>
       </c>
@@ -18075,7 +18073,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="480" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F480" s="4">
         <v>469</v>
       </c>
@@ -18084,7 +18082,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="481" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F481" s="4">
         <v>470</v>
       </c>
@@ -18093,7 +18091,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="482" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F482" s="4">
         <v>471</v>
       </c>
@@ -18102,7 +18100,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="483" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F483" s="4">
         <v>472</v>
       </c>
@@ -18111,7 +18109,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="484" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F484" s="4">
         <v>473</v>
       </c>
@@ -18120,7 +18118,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="485" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F485" s="4">
         <v>474</v>
       </c>
@@ -18129,7 +18127,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="486" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F486" s="4">
         <v>475</v>
       </c>
@@ -18138,7 +18136,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="487" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F487" s="4">
         <v>476</v>
       </c>
@@ -18147,7 +18145,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="488" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F488" s="4">
         <v>477</v>
       </c>
@@ -18156,7 +18154,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="489" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F489" s="4">
         <v>478</v>
       </c>
@@ -18165,7 +18163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="490" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F490" s="4">
         <v>479</v>
       </c>
@@ -18174,7 +18172,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="491" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F491" s="4">
         <v>480</v>
       </c>
@@ -18183,7 +18181,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="492" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F492" s="4">
         <v>481</v>
       </c>
@@ -18192,7 +18190,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="493" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F493" s="4">
         <v>482</v>
       </c>
@@ -18201,7 +18199,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="494" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F494" s="4">
         <v>483</v>
       </c>
@@ -18210,7 +18208,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="495" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F495" s="4">
         <v>484</v>
       </c>
@@ -18219,7 +18217,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="496" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F496" s="4">
         <v>485</v>
       </c>
@@ -18228,7 +18226,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="497" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F497" s="4">
         <v>486</v>
       </c>
@@ -18237,7 +18235,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="498" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F498" s="4">
         <v>487</v>
       </c>
@@ -18246,7 +18244,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="499" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F499" s="4">
         <v>488</v>
       </c>
@@ -18255,7 +18253,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="500" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F500" s="4">
         <v>489</v>
       </c>
@@ -18264,7 +18262,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="501" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F501" s="4">
         <v>490</v>
       </c>
@@ -18273,7 +18271,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="502" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F502" s="4">
         <v>491</v>
       </c>
@@ -18282,7 +18280,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="503" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F503" s="4">
         <v>492</v>
       </c>
@@ -18291,7 +18289,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="504" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F504" s="4">
         <v>493</v>
       </c>
@@ -18300,7 +18298,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="505" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F505" s="4">
         <v>494</v>
       </c>
@@ -18309,7 +18307,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="506" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F506" s="4">
         <v>495</v>
       </c>
@@ -18318,7 +18316,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="507" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F507" s="4">
         <v>496</v>
       </c>
@@ -18327,7 +18325,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="508" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F508" s="4">
         <v>497</v>
       </c>
@@ -18336,7 +18334,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="509" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F509" s="4">
         <v>498</v>
       </c>
@@ -18345,7 +18343,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="510" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F510" s="4">
         <v>499</v>
       </c>
@@ -18354,7 +18352,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="511" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F511" s="4">
         <v>500</v>
       </c>
@@ -18363,7 +18361,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="512" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F512" s="4">
         <v>501</v>
       </c>
@@ -18372,7 +18370,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="513" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F513" s="4">
         <v>502</v>
       </c>
@@ -18381,7 +18379,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="514" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F514" s="4">
         <v>503</v>
       </c>
@@ -18390,7 +18388,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="515" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F515" s="4">
         <v>504</v>
       </c>
@@ -18399,7 +18397,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="516" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F516" s="4">
         <v>505</v>
       </c>
@@ -18408,7 +18406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="517" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F517" s="4">
         <v>506</v>
       </c>
@@ -18417,7 +18415,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="518" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F518" s="4">
         <v>507</v>
       </c>
@@ -18426,7 +18424,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="519" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F519" s="4">
         <v>508</v>
       </c>
@@ -18435,7 +18433,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="520" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F520" s="4">
         <v>509</v>
       </c>
@@ -18444,7 +18442,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="521" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F521" s="4">
         <v>510</v>
       </c>
@@ -18453,7 +18451,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="522" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F522" s="4">
         <v>511</v>
       </c>
@@ -18462,7 +18460,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="523" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F523" s="4">
         <v>512</v>
       </c>
@@ -18471,7 +18469,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="524" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F524" s="4">
         <v>513</v>
       </c>
@@ -18480,7 +18478,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="525" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F525" s="4">
         <v>514</v>
       </c>
@@ -18489,7 +18487,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="526" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F526" s="4">
         <v>515</v>
       </c>
@@ -18498,7 +18496,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="527" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F527" s="4">
         <v>516</v>
       </c>
@@ -18507,7 +18505,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="528" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F528" s="4">
         <v>517</v>
       </c>
@@ -18516,7 +18514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="529" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F529" s="4">
         <v>518</v>
       </c>
@@ -18525,7 +18523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="530" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F530" s="4">
         <v>519</v>
       </c>
@@ -18534,7 +18532,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="531" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F531" s="4">
         <v>520</v>
       </c>
@@ -18543,7 +18541,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="532" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F532" s="4">
         <v>521</v>
       </c>
@@ -18552,7 +18550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="533" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F533" s="4">
         <v>522</v>
       </c>
@@ -18561,7 +18559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="534" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F534" s="4">
         <v>523</v>
       </c>
@@ -18570,7 +18568,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="535" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F535" s="4">
         <v>524</v>
       </c>
@@ -18579,7 +18577,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="536" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F536" s="4">
         <v>525</v>
       </c>
@@ -18588,7 +18586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="537" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F537" s="4">
         <v>526</v>
       </c>
@@ -18597,7 +18595,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="538" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F538" s="4">
         <v>527</v>
       </c>
@@ -18606,7 +18604,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="539" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F539" s="4">
         <v>528</v>
       </c>
@@ -18615,7 +18613,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="540" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F540" s="4">
         <v>529</v>
       </c>
@@ -18624,7 +18622,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="541" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F541" s="4">
         <v>530</v>
       </c>
@@ -18633,7 +18631,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="542" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F542" s="4">
         <v>531</v>
       </c>
@@ -18642,7 +18640,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="543" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F543" s="4">
         <v>532</v>
       </c>
@@ -18651,7 +18649,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="544" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F544" s="4">
         <v>533</v>
       </c>
@@ -18660,7 +18658,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="545" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F545" s="4">
         <v>534</v>
       </c>
@@ -18669,7 +18667,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="546" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="546" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F546" s="4">
         <v>535</v>
       </c>
@@ -18678,7 +18676,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="547" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="547" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F547" s="4">
         <v>536</v>
       </c>
@@ -18687,7 +18685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="548" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F548" s="4">
         <v>537</v>
       </c>
@@ -18696,7 +18694,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="549" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F549" s="4">
         <v>538</v>
       </c>
@@ -18705,7 +18703,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="550" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="550" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F550" s="4">
         <v>539</v>
       </c>
@@ -18714,7 +18712,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="551" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="551" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F551" s="4">
         <v>540</v>
       </c>
@@ -18723,7 +18721,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="552" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F552" s="4">
         <v>541</v>
       </c>
@@ -18732,7 +18730,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="553" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F553" s="4">
         <v>542</v>
       </c>
@@ -18741,7 +18739,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="554" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="554" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F554" s="4">
         <v>543</v>
       </c>
@@ -18750,7 +18748,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="555" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="555" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F555" s="4">
         <v>544</v>
       </c>
@@ -18759,7 +18757,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="556" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="556" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F556" s="4">
         <v>545</v>
       </c>
@@ -18768,7 +18766,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="557" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="557" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F557" s="4">
         <v>546</v>
       </c>
@@ -18777,7 +18775,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="558" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="558" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F558" s="4">
         <v>547</v>
       </c>
@@ -18786,7 +18784,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="559" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="559" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F559" s="4">
         <v>548</v>
       </c>
@@ -18795,7 +18793,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="560" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="560" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F560" s="4">
         <v>549</v>
       </c>
@@ -18804,7 +18802,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="561" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="561" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F561" s="4">
         <v>550</v>
       </c>
@@ -18813,7 +18811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="562" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="562" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F562" s="4">
         <v>551</v>
       </c>
@@ -18822,7 +18820,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="563" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="563" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F563" s="4">
         <v>552</v>
       </c>
@@ -18831,7 +18829,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="564" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="564" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F564" s="4">
         <v>553</v>
       </c>
@@ -18840,7 +18838,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="565" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="565" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F565" s="4">
         <v>554</v>
       </c>
@@ -18849,7 +18847,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="566" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="566" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F566" s="4">
         <v>555</v>
       </c>
@@ -18858,7 +18856,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="567" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="567" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F567" s="4">
         <v>556</v>
       </c>
@@ -18867,7 +18865,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="568" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="568" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F568" s="4">
         <v>557</v>
       </c>
@@ -18876,7 +18874,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="569" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="569" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F569" s="4">
         <v>558</v>
       </c>
@@ -18885,7 +18883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="570" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="570" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F570" s="4">
         <v>559</v>
       </c>
@@ -18894,7 +18892,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="571" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="571" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F571" s="4">
         <v>560</v>
       </c>
@@ -18903,7 +18901,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="572" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="572" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F572" s="4">
         <v>561</v>
       </c>
@@ -18912,7 +18910,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="573" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="573" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F573" s="4">
         <v>562</v>
       </c>
@@ -18921,7 +18919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="574" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="574" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F574" s="4">
         <v>563</v>
       </c>
@@ -18930,7 +18928,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="575" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="575" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F575" s="4">
         <v>564</v>
       </c>
@@ -18939,7 +18937,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="576" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="576" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F576" s="4">
         <v>565</v>
       </c>
@@ -18948,7 +18946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="577" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="577" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F577" s="4">
         <v>566</v>
       </c>
@@ -18957,7 +18955,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="578" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="578" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F578" s="4">
         <v>567</v>
       </c>
@@ -18966,7 +18964,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="579" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="579" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F579" s="4">
         <v>568</v>
       </c>
@@ -18975,7 +18973,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="580" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="580" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F580" s="4">
         <v>569</v>
       </c>
@@ -18984,7 +18982,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="581" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="581" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F581" s="4">
         <v>570</v>
       </c>
@@ -18993,7 +18991,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="582" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="582" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F582" s="4">
         <v>571</v>
       </c>
@@ -19002,7 +19000,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="583" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="583" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F583" s="4">
         <v>572</v>
       </c>
@@ -19011,7 +19009,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="584" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="584" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F584" s="4">
         <v>573</v>
       </c>
@@ -19020,7 +19018,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="585" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="585" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F585" s="4">
         <v>574</v>
       </c>
@@ -19029,7 +19027,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="586" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="586" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F586" s="4">
         <v>575</v>
       </c>
@@ -19038,7 +19036,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="587" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="587" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F587" s="4">
         <v>576</v>
       </c>
@@ -19047,7 +19045,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="588" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="588" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F588" s="4">
         <v>577</v>
       </c>
@@ -19056,7 +19054,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="589" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="589" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F589" s="4">
         <v>578</v>
       </c>
@@ -19065,7 +19063,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="590" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="590" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F590" s="4">
         <v>579</v>
       </c>
@@ -19074,7 +19072,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="591" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="591" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F591" s="4">
         <v>580</v>
       </c>
@@ -19083,7 +19081,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="592" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="592" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F592" s="4">
         <v>581</v>
       </c>
@@ -19092,7 +19090,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="593" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="593" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F593" s="4">
         <v>582</v>
       </c>
@@ -19101,7 +19099,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="594" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="594" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F594" s="4">
         <v>583</v>
       </c>
@@ -19110,7 +19108,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="595" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="595" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F595" s="4">
         <v>584</v>
       </c>
@@ -19119,7 +19117,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="596" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="596" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F596" s="4">
         <v>585</v>
       </c>
@@ -19128,7 +19126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="597" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="597" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F597" s="4">
         <v>586</v>
       </c>
@@ -19137,7 +19135,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="598" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="598" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F598" s="4">
         <v>587</v>
       </c>
@@ -19146,7 +19144,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="599" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="599" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F599" s="4">
         <v>588</v>
       </c>
@@ -19155,7 +19153,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="600" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="600" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F600" s="4">
         <v>589</v>
       </c>
@@ -19164,7 +19162,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="601" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="601" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F601" s="4">
         <v>590</v>
       </c>
@@ -19173,7 +19171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="602" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="602" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F602" s="4">
         <v>591</v>
       </c>
@@ -19182,7 +19180,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="603" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="603" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F603" s="4">
         <v>592</v>
       </c>
@@ -19191,7 +19189,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="604" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="604" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F604" s="4">
         <v>593</v>
       </c>
@@ -19200,7 +19198,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="605" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F605" s="4">
         <v>594</v>
       </c>
@@ -19209,7 +19207,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="606" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F606" s="4">
         <v>595</v>
       </c>
@@ -19218,7 +19216,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="607" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F607" s="4">
         <v>596</v>
       </c>
@@ -19227,7 +19225,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="608" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="608" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F608" s="4">
         <v>597</v>
       </c>
@@ -19236,7 +19234,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="609" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="609" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F609" s="4">
         <v>598</v>
       </c>
@@ -19245,7 +19243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="610" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="610" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F610" s="4">
         <v>599</v>
       </c>
@@ -19254,7 +19252,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="611" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="611" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F611" s="10">
         <v>600</v>
       </c>
